--- a/leads_dentista_campinas.xlsx
+++ b/leads_dentista_campinas.xlsx
@@ -491,12 +491,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Yandex Maps: search for places, transport, an</t>
+          <t>Dentistas em Campinas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yandex Maps: search for places, transport, and routes</t>
+          <t>Dentistas em Campinas - SP: 1383 avaliados · 4.8★ | DentMap</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yandex Maps will help you find your destination even if you don't have the exact address — get a rou...</t>
+          <t>No DentMap você pode comparar 1528 dentistas em Campinas por avaliações do Google, especialidade, ba...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -521,24 +521,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://yandex.com/maps/</t>
+          <t>https://dentmap.com.br/dentistas/campinas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Yandex%20Maps%3A%20search%20for%20places%2C%20transport%2C%20an%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentistas%20em%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Yandex Maps: search for places, transport, an aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentistas em Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -548,29 +548,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Yandex Maps: search for places, transport, an?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentistas em Campinas?</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Yandex%20Maps%3A%20search%20for%20places%2C%20transport%2C%20an%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentistas%20em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Yandex%20Maps%3A%20search%20for%20places%2C%20transport%2C%20an%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentistas%20em%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dentistas em Campinas: Ache o melhor</t>
+          <t>Dra. Lvia Sousa, Dentista, R. Tiradentes, 446</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dentistas em Campinas: Ache o melhor | Agende sua consulta com...</t>
+          <t>Dra. Lívia Sousa, Dentista, R. Tiradentes, 446 - Jardim ...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ache o melhor Dentistas com avaliações, preços dos serviços, anos de experiência em Campinas e agend...</t>
+          <t>Lívia Sousa, Dentista, São Paulo, comentários de clientes, mapa de localização, números de telefone,...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.doctoranytime.com.br/s/dentista/campinas</t>
+          <t>https://brasillocais.com/sao-paulo/dra-livia-sousa-1176627</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentistas%20em%20Campinas%3A%20Ache%20o%20melhor%20campinas</t>
+          <t>https://www.google.com/maps/search/Dra.%20Lvia%20Sousa%2C%20Dentista%2C%20R.%20Tiradentes%2C%20446%20campinas</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentistas em Campinas: Ache o melhor aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dra. Lvia Sousa, Dentista, R. Tiradentes, 446 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -622,17 +622,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentistas em Campinas: Ache o melhor?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dra. Lvia Sousa, Dentista, R. Tiradentes, 446?</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentistas%20em%20Campinas%3A%20Ache%20o%20melhor%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dra.%20Lvia%20Sousa%2C%20Dentista%2C%20R.%20Tiradentes%2C%20446%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentistas%20em%20Campinas%3A%20Ache%20o%20melhor%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dra.%20Lvia%20Sousa%2C%20Dentista%2C%20R.%20Tiradentes%2C%20446%3F</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -701,12 +701,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Odontolgica%20Odonthos%20Odontologia%20Campi%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Odontolgica%20Odonthos%20Odontologia%20Campi%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Odontolgica%20Odonthos%20Odontologia%20Campi%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Odontolgica%20Odonthos%20Odontologia%20Campi%3F</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -775,24 +775,24 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Especialista%20em%20Implantes%20Dentrios%20em%20Campina%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Especialista%20em%20Implantes%20Dentrios%20em%20Campina%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Especialista%20em%20Implantes%20Dentrios%20em%20Campina%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Especialista%20em%20Implantes%20Dentrios%20em%20Campina%3F</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dentista em Campinas Centro Mdico Sade Acessv</t>
+          <t>Dentistas em Centro, Campinas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dentista em Campinas Centro Médico Saúde Acessível | Consultare</t>
+          <t>Dentistas em Centro, Campinas - SP | DentMap</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Agendamento com DENTISTA em Campinas no melhor Centro Médico de Saúde acessível do Brasil, a Consult...</t>
+          <t>Encontre dentistas em Centro, Campinas. Compare avaliacoes, especialidades e agende sua consulta no ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -817,24 +817,28 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.consultare.com.br/dentista-campinas</t>
+          <t>https://dentmap.com.br/dentistas/campinas?especialidade=clinico-geral&amp;bairro=Centro&amp;pagina=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(19) 3326-1410</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>551933261410</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentista%20em%20Campinas%20Centro%20Mdico%20Sade%20Acessv%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentistas%20em%20Centro%2C%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentista em Campinas Centro Mdico Sade Acessv aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentistas em Centro, Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -844,29 +848,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentista em Campinas Centro Mdico Sade Acessv?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentistas em Centro, Campinas?</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentista%20em%20Campinas%20Centro%20Mdico%20Sade%20Acessv%20campinas%20whatsapp</t>
+          <t>https://wa.me/551933261410?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentistas%20em%20Centro%2C%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentista%20em%20Campinas%20Centro%20Mdico%20Sade%20Acessv%20campinas%20whatsapp</t>
+          <t>https://wa.me/551933261410?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentistas%20em%20Centro%2C%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dentista Campinas</t>
+          <t>Dentista e Odontologia Especializada em Campi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dentista Campinas | Transformando Sorrisos e Vidas - Home</t>
+          <t>Dentista e Odontologia Especializada em Campinas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -881,34 +885,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trustindex verifica se a fonte original da avaliação é Google. Ótima dentista. Atenciosa e muito cui...</t>
+          <t>Em 2011, após todo um processo de seleção de cidades e locais, foi construída dentro das mais novas ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://dentistacampinas.com.br/</t>
+          <t>https://greghiodontologia.com.br/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentista%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentista%20e%20Odontologia%20Especializada%20em%20Campi%20campinas</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentista Campinas aí em Campinas no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da Dentista e Odontologia Especializada em Campi aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -918,29 +922,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentista Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista e Odontologia Especializada em Campi?</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentista%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20e%20Odontologia%20Especializada%20em%20Campi%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentista%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%20e%20Odontologia%20Especializada%20em%20Campi%3F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dentista e Odontologia Especializada em Campi</t>
+          <t>10 melhores dentistas para Campinas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dentista e Odontologia Especializada em Campinas</t>
+          <t>10 melhores dentistas para Campinas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -955,7 +959,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Em 2011, após todo um processo de seleção de cidades e locais, foi construída dentro das mais novas ...</t>
+          <t>Nossos melhores dentistas em Campinas, avaliados pela comunidade StarOfService - Campinas, São Paulo...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -965,28 +969,28 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://greghiodontologia.com.br/</t>
+          <t>https://www.starofservice.com.br/dir/sao-paulo/campinas/campinas/servicos-dentarios</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>19 98127-8626</t>
+          <t>(19) 97419-5901</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>551998127862600</t>
+          <t>5519974195901</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentista%20e%20Odontologia%20Especializada%20em%20Campi%20campinas</t>
+          <t>https://www.google.com/maps/search/10%20melhores%20dentistas%20para%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentista e Odontologia Especializada em Campi aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 10 melhores dentistas para Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -996,29 +1000,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentista e Odontologia Especializada em Campi?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 10 melhores dentistas para Campinas?</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://wa.me/551998127862600?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20e%20Odontologia%20Especializada%20em%20Campi%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519974195901?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2010%20melhores%20dentistas%20para%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://wa.me/551998127862600?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%20e%20Odontologia%20Especializada%20em%20Campi%3F</t>
+          <t>https://wa.me/5519974195901?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2010%20melhores%20dentistas%20para%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Odontologia Vetorasso</t>
+          <t>Dentista 24 Horas Campinas (19) 9 9409-5553</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Odontologia Vetorasso | dentista campinas | Rua Barata Ribeiro, 5</t>
+          <t>Dentista 24 Horas Campinas (19) 9 9409-5553 Whatsapp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1033,7 +1037,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dentista em Campinas, Odontologia Vetorasso, há mais de 40 anos cuidando do seu sorriso.Bem-vindo ao...</t>
+          <t>logo dentista 24horas campinas. Rua Jerônimo Páttaro 364 – Barão Geraldo – Campinas SP.Chamar no Wha...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1043,28 +1047,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.odontologiavetorasso.com/</t>
+          <t>https://dentista24horascampinas.com.br/</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(17) 99148-5455</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>551799148545500</t>
-        </is>
-      </c>
+          <t>(CA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Odontologia%20Vetorasso%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%20campinas</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odontologia Vetorasso aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentista 24 Horas Campinas (19) 9 9409-5553 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1074,29 +1074,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odontologia Vetorasso?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista 24 Horas Campinas (19) 9 9409-5553?</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://wa.me/551799148545500?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20Vetorasso%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://wa.me/551799148545500?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%20Vetorasso%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%3F</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Contato</t>
+          <t>Os Melhores Dentistas em Campinas, SP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Contato | Dentista Campinas</t>
+          <t>Os Melhores Dentistas em Campinas, SP — WhatsApp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1111,38 +1111,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dentista em Campinas. Onde Atendemos Sobre Contato.WhatsApp: WhatsApp (11) 95213-7463. E-mail: conta...</t>
+          <t>Veja os dentistas mais bem avaliados em Campinas, SP. Clareamento, implantes, ortodontia, limpeza, r...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://campinasdentista.com.br/contato/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(11) 95213-7463</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>551195213746300</t>
-        </is>
-      </c>
+          <t>(CA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Contato%20campinas</t>
+          <t>https://www.google.com/maps/search/Os%20Melhores%20Dentistas%20em%20Campinas%2C%20SP%20campinas</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Contato aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Os Melhores Dentistas em Campinas, SP aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1152,29 +1148,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Contato?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Os Melhores Dentistas em Campinas, SP?</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://wa.me/551195213746300?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Contato%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Os%20Melhores%20Dentistas%20em%20Campinas%2C%20SP%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://wa.me/551195213746300?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Contato%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Os%20Melhores%20Dentistas%20em%20Campinas%2C%20SP%3F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ana Carolina Diniz</t>
+          <t>Dra Camila Roberta</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ana Carolina Diniz - Dentista Campinas - SP</t>
+          <t>Dra Camila Roberta - Odontologia | Campinas SP - FacebookConsultó</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1189,34 +1185,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ana Carolina é Cirurgiã-Dentista com graduação em Odontologia e pós-graduação em Implantodontia. Apa...</t>
+          <t>Realizamos a gengivoplastia, ajustando o contorno da gengiva, e finalizamos com o clareamento dental...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.anacarolinadiniz.com/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Ana%20Carolina%20Diniz%20campinas</t>
+          <t>https://www.google.com/maps/search/Dra%20Camila%20Roberta%20campinas</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Ana Carolina Diniz aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dra Camila Roberta aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1226,29 +1222,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Ana Carolina Diniz?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dra Camila Roberta?</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Ana%20Carolina%20Diniz%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dra%20Camila%20Roberta%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Ana%20Carolina%20Diniz%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dra%20Camila%20Roberta%3F</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Agente IA</t>
+          <t>Consultrio Dentrio 24 Horas Campinas (19) 9 9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Agente IA WhatsApp para Consultorio Odontologico em Campinas...</t>
+          <t>Consultório Dentário 24 Horas Campinas (19) 9 9409-5553 Whatsapp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1263,7 +1259,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Se você tem um consultório odontologico em Campinas, sabe que WhatsApp e o principal canal de contat...</t>
+          <t>Consultório Dentário 24 Horas Campinas (19) 9 9409-5553 Whatsapp Consultório Dentário 24 Horas Campi...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1273,24 +1269,28 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://atendente24h.com/cidades/sp/campinas/dentista.html</t>
+          <t>https://dentista24horascampinas.com.br/consultorio-dentario-24-horas-campinas/</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(19) 99409-5553</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5519994095553</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Agente%20IA%20campinas</t>
+          <t>https://www.google.com/maps/search/Consultrio%20Dentrio%2024%20Horas%20Campinas%20%2819%29%209%209%20campinas</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Agente IA aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Consultrio Dentrio 24 Horas Campinas (19) 9 9 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1300,29 +1300,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Agente IA?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Consultrio Dentrio 24 Horas Campinas (19) 9 9?</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Agente%20IA%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519994095553?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consultrio%20Dentrio%2024%20Horas%20Campinas%20%2819%29%209%209%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Agente%20IA%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519994095553?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consultrio%20Dentrio%2024%20Horas%20Campinas%20%2819%29%209%209%3F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dentistas em Centro, Campinas</t>
+          <t>Ana Carolina Diniz</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dentistas em Centro, Campinas - SP | DentMap</t>
+          <t>Ana Carolina Diniz - Dentista Campinas - SP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Encontre os melhores dentistas em Centro, Campinas. Compare avaliações, especialidades e agende sua ...</t>
+          <t>Ana Carolina é Cirurgiã-Dentista com graduação em Odontologia e pós-graduação em Implantodontia. Apa...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1347,24 +1347,28 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://dentmap.com.br/dentistas/campinas/centro</t>
+          <t>https://www.anacarolinadiniz.com/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(19) 98332-9496</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5519983329496</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentistas%20em%20Centro%2C%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Ana%20Carolina%20Diniz%20campinas</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentistas em Centro, Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Ana Carolina Diniz aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1374,29 +1378,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentistas em Centro, Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Ana Carolina Diniz?</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentistas%20em%20Centro%2C%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519983329496?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Ana%20Carolina%20Diniz%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentistas%20em%20Centro%2C%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519983329496?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Ana%20Carolina%20Diniz%3F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Odontoclinic Campinas</t>
+          <t>Odontologia Vetorasso</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Odontoclinic Campinas - Dentista no Campo Grande</t>
+          <t>Odontologia Vetorasso | dentista campinas | Rua Barata Ribeiro, 5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,7 +1415,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A clínica mais procurada da região de Campo Grande - Campinas - pelo atendimento de qualidade do tra...</t>
+          <t>Dentista em Campinas, Odontologia Vetorasso, há mais de 40 anos cuidando do seu sorriso.Bem-vindo ao...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1421,24 +1425,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://dentistanocampogrande.com.br/</t>
+          <t>https://www.odontologiavetorasso.com/</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Odontoclinic%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Odontologia%20Vetorasso%20campinas</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odontoclinic Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Odontologia Vetorasso aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1448,29 +1452,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odontoclinic Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odontologia Vetorasso?</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Odontoclinic%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20Vetorasso%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Odontoclinic%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%20Vetorasso%3F</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Clnica Synergia</t>
+          <t>Odontoclinic Campinas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clínica Synergia – Cuidados Odontológicos</t>
+          <t>Odontoclinic Campinas - Dentista no Campo Grande</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Agende via WhatsApp. Na Clínica Synergia, cada detalhe é pensado para proporcionar tratamentos perso...</t>
+          <t>A clínica mais procurada da região de Campo Grande - Campinas - pelo atendimento de qualidade do tra...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1495,24 +1499,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://clinicasynergia.com.br/</t>
+          <t>https://dentistanocampogrande.com.br/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Synergia%20campinas</t>
+          <t>https://www.google.com/maps/search/Odontoclinic%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Synergia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Odontoclinic Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1522,29 +1526,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Synergia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odontoclinic Campinas?</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Synergia%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontoclinic%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Synergia%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontoclinic%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>Sculpere Clnica Odontolgica</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>Sculpere Clínica Odontológica - Campinas - SP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1559,34 +1563,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The site owner hides the web page description....</t>
+          <t>Dentista Campinas. Home. Clínica.Acreditamos que o resultado de um tratamento é altamente dependente...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://sculpere.com.br/</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>19982555</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5519982555</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Link%20to%20instagram.com%20campinas</t>
+          <t>https://www.google.com/maps/search/Sculpere%20Clnica%20Odontolgica%20campinas</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to instagram.com aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Sculpere Clnica Odontolgica aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1596,29 +1604,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to instagram.com?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Sculpere Clnica Odontolgica?</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Link%20to%20instagram.com%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519982555?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Sculpere%20Clnica%20Odontolgica%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Link%20to%20instagram.com%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519982555?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Sculpere%20Clnica%20Odontolgica%3F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Clnica Odontolgica Smile Center Campinas</t>
+          <t>Odontologia Campinas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clínica Odontológica Smile Center Campinas</t>
+          <t>Odontologia Campinas | Artesania | Studio Oral Campinas | Brasil</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1633,7 +1641,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A clínica odontológica Smile Center Campinas tem como objetivo o atendimento multidisciplinar, integ...</t>
+          <t>restauracao e proteses dentista campinas. Restaurações. e Próteses. bruxismo dental em campinas.png....</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1643,24 +1651,28 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://smilecampinas.com.br/</t>
+          <t>https://www.artesaniaoral.com/</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(19) 3242-4670</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>551932424670</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Odontolgica%20Smile%20Center%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Odontologia%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Odontolgica Smile Center Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Odontologia Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1670,29 +1682,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Odontolgica Smile Center Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odontologia Campinas?</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Odontolgica%20Smile%20Center%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/551932424670?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Odontolgica%20Smile%20Center%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/551932424670?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dentistas</t>
+          <t>Clnica Odontolgica Em Campinas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dentistas | Implantes Protocolo | Ortodontia</t>
+          <t>Clínica Odontológica Em Campinas | Intégra Odontologia E Saúde</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1707,7 +1719,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Clínica Sorriso de Campinas – Qualidade que cabe no seu bolso! Implantes, próteses, aparelhos e muit...</t>
+          <t>Não se preocupe, aqui na Intégra Odontologia e Saúde, você será atendido pelos melhores dentistas de...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1717,24 +1729,28 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.sorrisodecampinas.com/</t>
+          <t>https://www.integraodontosaude.com.br/</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(19) 3326-1406</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>551933261406</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentistas%20campinas</t>
+          <t>https://www.google.com/maps/search/Clnica%20Odontolgica%20Em%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentistas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica Odontolgica Em Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1744,29 +1760,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentistas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Odontolgica Em Campinas?</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentistas%20campinas%20whatsapp</t>
+          <t>https://wa.me/551933261406?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Odontolgica%20Em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentistas%20campinas%20whatsapp</t>
+          <t>https://wa.me/551933261406?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Odontolgica%20Em%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OdontoCampinas</t>
+          <t>Consultrio Odontolgico Mariana Szatkovski 5.0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OdontoCampinas</t>
+          <t>Consultório Odontológico Mariana Szatkovski · 5.0★ (59 ...</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1781,7 +1797,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Com mais de 10 anos de experiência e mais de 1000 sorrisos atendidos, somos sua escolha confiável pa...</t>
+          <t>O contato pode ser feito por telefone ou WhatsApp diretamente pela página do profissional. Use o Den...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1791,28 +1807,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>http://www.odontocampinas.com.br/</t>
+          <t>https://dentmap.com.br/dentistas/campinas/consultorio-odontologico-mariana-szatkovski-4fgdphyq</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(19) 98765-7174</t>
+          <t>(19) 2116-0156</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>551998765717400</t>
+          <t>551921160156</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/OdontoCampinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Consultrio%20Odontolgico%20Mariana%20Szatkovski%205.0%20campinas</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da OdontoCampinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Consultrio Odontolgico Mariana Szatkovski 5.0 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1822,29 +1838,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a OdontoCampinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Consultrio Odontolgico Mariana Szatkovski 5.0?</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://wa.me/551998765717400?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OdontoCampinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551921160156?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consultrio%20Odontolgico%20Mariana%20Szatkovski%205.0%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://wa.me/551998765717400?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OdontoCampinas%3F</t>
+          <t>https://wa.me/551921160156?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consultrio%20Odontolgico%20Mariana%20Szatkovski%205.0%3F</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sculpere Clnica Odontolgica</t>
+          <t>Clnica Synergia</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sculpere Clínica Odontológica - Campinas - SP</t>
+          <t>Clínica Synergia – Cuidados Odontológicos</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1859,7 +1875,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dentista Campinas. Home. Clínica.Acreditamos que o resultado de um tratamento é altamente dependente...</t>
+          <t>Agende via WhatsApp. Na Clínica Synergia, cada detalhe é pensado para proporcionar tratamentos perso...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1869,28 +1885,28 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://sculpere.com.br/</t>
+          <t>https://clinicasynergia.com.br/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19 98255-5790</t>
+          <t>19323129</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>551998255579000</t>
+          <t>5519323129</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Sculpere%20Clnica%20Odontolgica%20campinas</t>
+          <t>https://www.google.com/maps/search/Clnica%20Synergia%20campinas</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Sculpere Clnica Odontolgica aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica Synergia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1900,29 +1916,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Sculpere Clnica Odontolgica?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Synergia?</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://wa.me/551998255579000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Sculpere%20Clnica%20Odontolgica%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519323129?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Synergia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://wa.me/551998255579000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Sculpere%20Clnica%20Odontolgica%3F</t>
+          <t>https://wa.me/5519323129?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Synergia%3F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10 melhores dentistas para Campinas</t>
+          <t>Link to instagram.com</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10 melhores dentistas para Campinas</t>
+          <t>Link to instagram.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1937,34 +1953,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dentista. 13023-490 Campinas. A clinica integra vários dentistas, e cada um cuida de uma especialida...</t>
+          <t>The site owner hides the web page description....</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.starofservice.com.br/dir/sao-paulo/campinas/campinas/servicos-dentarios</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/10%20melhores%20dentistas%20para%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Link%20to%20instagram.com%20campinas</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 10 melhores dentistas para Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Link to instagram.com aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1974,29 +1990,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 10 melhores dentistas para Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Link to instagram.com?</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=10%20melhores%20dentistas%20para%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20instagram.com%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=10%20melhores%20dentistas%20para%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20instagram.com%3F</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dentista</t>
+          <t>Procure seu Dentista</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dentista | Campinas | Intégra Odontologia &amp; Saúde</t>
+          <t>Procure seu Dentista - Uniodonto</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2011,7 +2027,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dentistas Mestre e Especialistas para cuidar de você com dedicação e carinho. A Intégra Odontologia ...</t>
+          <t>Procure de forma rápida e fácil seu dentista cooperado da Uniodonto Campinas. Utilize os filtros e r...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2021,24 +2037,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.integraodontosaude.com.br/dentista</t>
+          <t>https://www.uniodontocampinas.com.br/procure-seu-dentista/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentista%20campinas</t>
+          <t>https://www.google.com/maps/search/Procure%20seu%20Dentista%20campinas</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentista aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Procure seu Dentista aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2048,17 +2064,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentista?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Procure seu Dentista?</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentista%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Procure%20seu%20Dentista%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentista%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Procure%20seu%20Dentista%3F</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2116,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2127,24 +2143,24 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Dentista%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Dentista%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Dentista%20Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Dentista%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Elegance Sorriso</t>
+          <t>Clnica Odontolgica Smile Center Campinas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Elegance Sorriso — Clínica Odontológica em Campinas</t>
+          <t>Clínica Odontológica Smile Center Campinas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2159,7 +2175,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Elegance Sorriso — clínica odontológica em Campinas com 4 unidades. Implantes, ortodontia, clareamen...</t>
+          <t>A clínica odontológica Smile Center Campinas tem como objetivo o atendimento multidisciplinar, integ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2169,28 +2185,28 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://elegancesorriso.com.br/</t>
+          <t>https://smilecampinas.com.br/</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(19) 3012-2993</t>
+          <t>(19) 3241-1840</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>55193012299300</t>
+          <t>551932411840</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Elegance%20Sorriso%20campinas</t>
+          <t>https://www.google.com/maps/search/Clnica%20Odontolgica%20Smile%20Center%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Elegance Sorriso aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica Odontolgica Smile Center Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2200,29 +2216,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Elegance Sorriso?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Odontolgica Smile Center Campinas?</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://wa.me/55193012299300?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Elegance%20Sorriso%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551932411840?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Odontolgica%20Smile%20Center%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://wa.me/55193012299300?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Elegance%20Sorriso%3F</t>
+          <t>https://wa.me/551932411840?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Odontolgica%20Smile%20Center%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Campinas</t>
+          <t>OdontoCampinas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Campinas – Guanabara - Odontoclinic</t>
+          <t>OdontoCampinas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2237,7 +2253,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dentista em Campinas – Guanabara. Entendemos que a estética do sorriso tem muito impacto na autoimag...</t>
+          <t>Com mais de 10 anos de experiência e mais de 1000 sorrisos atendidos, somos sua escolha confiável pa...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2247,24 +2263,28 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://odontoclinic.com.br/unidades/campinas-guanabara/?step=1</t>
+          <t>http://www.odontocampinas.com.br/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(19) 98765-7174</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5519987657174</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/OdontoCampinas%20campinas</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da OdontoCampinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2274,29 +2294,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a OdontoCampinas?</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519987657174?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OdontoCampinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Campinas%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519987657174?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OdontoCampinas%3F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Procure seu Dentista</t>
+          <t>Dentistas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Procure seu Dentista - Uniodonto</t>
+          <t>Dentistas | Implantes Protocolo | Ortodontia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2311,7 +2331,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Procure de forma rápida e fácil seu dentista cooperado da Uniodonto Campinas. Utilize os filtros e r...</t>
+          <t>Clínica Sorriso de Campinas – Qualidade que cabe no seu bolso! Implantes, próteses, aparelhos e muit...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2321,24 +2341,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.uniodontocampinas.com.br/procure-seu-dentista/</t>
+          <t>https://www.sorrisodecampinas.com/</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Procure%20seu%20Dentista%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentistas%20campinas</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Procure seu Dentista aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentistas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2348,17 +2368,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Procure seu Dentista?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentistas?</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Procure%20seu%20Dentista%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentistas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Procure%20seu%20Dentista%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentistas%3F</t>
         </is>
       </c>
     </row>
@@ -2400,10 +2420,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(19) 3045-9140</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>551930459140</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Principal%20campinas</t>
@@ -2427,24 +2451,24 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Principal%20campinas%20whatsapp</t>
+          <t>https://wa.me/551930459140?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Principal%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Principal%20campinas%20whatsapp</t>
+          <t>https://wa.me/551930459140?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Principal%3F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dentista 24 Horas Campinas (19) 9 9409-5553</t>
+          <t>Dentista em Campinas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dentista 24 Horas Campinas (19) 9 9409-5553 Whatsapp</t>
+          <t>Dentista em Campinas | Particular | Dr. Edi - Vida Odontologia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2459,7 +2483,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>logo dentista 24horas campinas. Rua Jerônimo Páttaro 364 – Barão Geraldo – Campinas SP.inclusive aos...</t>
+          <t>Dentista particular em Campinas com mais de 20 anos de experiência. Especialista em implantes, próte...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2469,28 +2493,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://dentista24horascampinas.com.br/</t>
+          <t>https://dredi.com.br/dentista/campinas/</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(19) 99409-5553</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>551999409555300</t>
-        </is>
-      </c>
+          <t>(CA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentista%20em%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentista 24 Horas Campinas (19) 9 9409-5553 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentista em Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2500,29 +2520,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentista 24 Horas Campinas (19) 9 9409-5553?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista em Campinas?</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://wa.me/551999409555300?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://wa.me/551999409555300?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%20em%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rhema Clnica Odontologia</t>
+          <t>Dentista 24 Horas em Campinas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rhema Clínica Odontologia | Dentista em Campinas | Av Ten ...</t>
+          <t>Dentista 24 Horas em Campinas | Dentista 24 Horas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2537,7 +2557,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Entre em contato conosco hoje mesmo para agendar uma consulta e experimentar a diferença que nossa c...</t>
+          <t>Dentista 24 horas em Campinas/SP. Atendimento de urgência e tratamentos completos em várias especial...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2547,28 +2567,28 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.rhemaclinica.com/</t>
+          <t>https://www.villeladentista.com.br/</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1255004600</t>
+          <t>(11) 3089-6060</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>55125500460000</t>
+          <t>551130896060</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Rhema%20Clnica%20Odontologia%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentista%2024%20Horas%20em%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Rhema Clnica Odontologia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentista 24 Horas em Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2578,29 +2598,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Rhema Clnica Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista 24 Horas em Campinas?</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://wa.me/55125500460000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Rhema%20Clnica%20Odontologia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551130896060?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%2024%20Horas%20em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://wa.me/55125500460000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Rhema%20Clnica%20Odontologia%3F</t>
+          <t>https://wa.me/551130896060?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%2024%20Horas%20em%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Emergncia Odontolgica em Campinas 24h</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Home - Uniodonto</t>
+          <t>Emergência Odontológica em Campinas 24h | Dra. Silvia Satriuc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2615,7 +2635,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Os planos odontológicos da Uniodonto Campinas oferecem dentistas, cirurgiões e clínicas de alto padr...</t>
+          <t>Dentista em Campinas. Emergência Odontológica Plantão das 7hs as 23hs.Melhorias estéticas no sorriso...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2625,28 +2645,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.uniodontocampinas.com.br/</t>
+          <t>https://silviasatriuc.com.br/</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(19) 3241-3305</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>55193241330500</t>
-        </is>
-      </c>
+          <t>(CA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Home%20campinas</t>
+          <t>https://www.google.com/maps/search/Emergncia%20Odontolgica%20em%20Campinas%2024h%20campinas</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Home aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Emergncia Odontolgica em Campinas 24h aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2656,29 +2672,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Home?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Emergncia Odontolgica em Campinas 24h?</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://wa.me/55193241330500?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Home%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Emergncia%20Odontolgica%20em%20Campinas%2024h%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://wa.me/55193241330500?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Home%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Emergncia%20Odontolgica%20em%20Campinas%2024h%3F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Google Maps Campinas: atraia pacientes</t>
+          <t>Dra. Anita Monteiro</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Google Maps Campinas: atraia pacientes</t>
+          <t>Dra. Anita Monteiro - Dentista Campinas, odontologia e mais</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2693,7 +2709,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Como aparecer no Google Maps em Campinas e atrair pacientes. Foto do escritor: gil celidonio....</t>
+          <t>Um atendimento acolhedor, cheio de profissionalismo e cuidado, moro em Indaiatuba e faço questão de ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2703,24 +2719,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.creisconsultoria.com/post/google-maps-campinas-pacientes-2</t>
+          <t>https://odontologiamonteiro.com.br/</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Google%20Maps%20Campinas%3A%20atraia%20pacientes%20campinas</t>
+          <t>https://www.google.com/maps/search/Dra.%20Anita%20Monteiro%20campinas</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Google Maps Campinas: atraia pacientes aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dra. Anita Monteiro aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2730,29 +2746,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Google Maps Campinas: atraia pacientes?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dra. Anita Monteiro?</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Google%20Maps%20Campinas%3A%20atraia%20pacientes%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dra.%20Anita%20Monteiro%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Google%20Maps%20Campinas%3A%20atraia%20pacientes%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dra.%20Anita%20Monteiro%3F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Como RASTREAR un CELULAR por GOOGLE MAPS...</t>
+          <t>Dentista</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Como RASTREAR un CELULAR por GOOGLE MAPS... - YouTube</t>
+          <t>Dentista | Campinas | Intégra Odontologia &amp; Saúde</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2767,34 +2783,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hoy te enseñaré como rastrear un celular por google maps con varios dispositivos tecnológicos.Espero...</t>
+          <t>Dentistas Mestre e Especialistas para cuidar de você com dedicação e carinho. A Intégra Odontologia ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.integraodontosaude.com.br/dentista</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Como%20RASTREAR%20un%20CELULAR%20por%20GOOGLE%20MAPS...%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentista%20campinas</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Como RASTREAR un CELULAR por GOOGLE MAPS... aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Dentista aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2804,29 +2820,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Como RASTREAR un CELULAR por GOOGLE MAPS...?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista?</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Como%20RASTREAR%20un%20CELULAR%20por%20GOOGLE%20MAPS...%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Como%20RASTREAR%20un%20CELULAR%20por%20GOOGLE%20MAPS...%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%3F</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Instant Google Street View</t>
+          <t>Rhema Clnica Odontologia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Instant Google Street View</t>
+          <t>Rhema Clínica Odontologia | Dentista em Campinas | Av Ten ...</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2841,7 +2857,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Instantly see a Google Street View of any supported location....</t>
+          <t>Entre em contato conosco hoje mesmo para agendar uma consulta e experimentar a diferença que nossa c...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2851,24 +2867,28 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.instantstreetview.com/</t>
+          <t>https://www.rhemaclinica.com/</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>19324150</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5519324150</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Instant%20Google%20Street%20View%20campinas</t>
+          <t>https://www.google.com/maps/search/Rhema%20Clnica%20Odontologia%20campinas</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Instant Google Street View aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Rhema Clnica Odontologia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2878,29 +2898,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Instant Google Street View?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Rhema Clnica Odontologia?</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Instant%20Google%20Street%20View%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519324150?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Rhema%20Clnica%20Odontologia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Instant%20Google%20Street%20View%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519324150?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Rhema%20Clnica%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>lifewire.com/get-street-view-google-maps-5197</t>
+          <t>A Barbearia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>lifewire.com/get-street-view-google-maps-5197819</t>
+          <t>A Barbearia – A melhor barbearia da Campinas!</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2915,7 +2935,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>How to Get Street View on Google Maps - Lifewire lifewire.com....</t>
+          <t>A Barbearia – A melhor barbearia da Campinas!...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2925,24 +2945,28 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.lifewire.com/get-street-view-google-maps-5197819</t>
+          <t>https://www.abarbearia.net/</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(19) 98990-7633</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5519989907633</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/lifewire.com/get-street-view-google-maps-5197%20campinas</t>
+          <t>https://www.google.com/maps/search/A%20Barbearia%20campinas</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da lifewire.com/get-street-view-google-maps-5197 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da A Barbearia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2952,29 +2976,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a lifewire.com/get-street-view-google-maps-5197?</t>
+Posso te mandar a prévia demonstrativa que fiz para a A Barbearia?</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=lifewire.com/get-street-view-google-maps-5197%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519989907633?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20A%20Barbearia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=lifewire.com/get-street-view-google-maps-5197%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519989907633?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20A%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ham Radio Maidenhead Grid Square Locator Geoc</t>
+          <t>Penny Lane Barbearia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ham Radio Maidenhead Grid Square Locator Geocoding with Google...</t>
+          <t>Penny Lane Barbearia | Barbearia Premium em Campinas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2989,34 +3013,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Enter 6 character grid square or Enter locality or Click on the map!...</t>
+          <t>Corte masculino, barba, prótese capilar, visagismo e atendimento VIP para noivos. A barbearia referê...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://dxcluster.ha8tks.hu/hamgeocoding/</t>
+          <t>https://www.pennylanebarbearia.com.br/</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Ham%20Radio%20Maidenhead%20Grid%20Square%20Locator%20Geoc%20campinas</t>
+          <t>https://www.google.com/maps/search/Penny%20Lane%20Barbearia%20campinas</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Ham Radio Maidenhead Grid Square Locator Geoc aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Penny Lane Barbearia aí em Campinas no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3026,29 +3050,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Ham Radio Maidenhead Grid Square Locator Geoc?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Penny Lane Barbearia?</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Ham%20Radio%20Maidenhead%20Grid%20Square%20Locator%20Geoc%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Penny%20Lane%20Barbearia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Ham%20Radio%20Maidenhead%20Grid%20Square%20Locator%20Geoc%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Penny%20Lane%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Encontrar seu smartphone</t>
+          <t>Barbearia Campinas Centro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Encontrar seu smartphone</t>
+          <t>Barbearia Campinas Centro - Campinas - SP - Guiamapa.com</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3063,34 +3087,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Configurações da Conta do Google. Ajuda. Fazer login....</t>
+          <t>Veja onde fica e como chegar em Barbearia Campinas utilizando nosso mapa e confira informações adici...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://guiamapa.com/onde-fica/barbearia-campinas/campinas/sp/92911</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(19) 98604-9825</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5519986049825</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Encontrar%20seu%20smartphone%20campinas</t>
+          <t>https://www.google.com/maps/search/Barbearia%20Campinas%20Centro%20campinas</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Encontrar seu smartphone aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Barbearia Campinas Centro aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3100,29 +3128,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Encontrar seu smartphone?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Campinas Centro?</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Encontrar%20seu%20smartphone%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519986049825?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Campinas%20Centro%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Encontrar%20seu%20smartphone%20campinas%20whatsapp</t>
+          <t>https://wa.me/5519986049825?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Campinas%20Centro%3F</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BARBARA CAMPINA ALVES 70448996413</t>
+          <t>10 Melhores Barbearias em Campinas</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BARBARA CAMPINA ALVES 70448996413 — CNPJ... | Sr. Watson</t>
+          <t>10 Melhores Barbearias em Campinas — Guia 2026 | Beard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3137,7 +3165,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Abrir no Google Maps.›Qual o(s) CNAE(s) da empresa BARBARA CAMPINA ALVES 70448996413? O CNAE princip...</t>
+          <t>Se você está em busca de um bom barbeiro em Campinas, este guia reúne as 10 melhores opções avaliada...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3147,28 +3175,28 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://srwatson.io/empresa/barbara-campina-alves-70448996413-40162396000198</t>
+          <t>https://blog.beard.com.br/barbearias-em-campinas/</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7044899641</t>
+          <t>(19) 3294-1717</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>55704489964100</t>
+          <t>551932941717</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/BARBARA%20CAMPINA%20ALVES%2070448996413%20campinas</t>
+          <t>https://www.google.com/maps/search/10%20Melhores%20Barbearias%20em%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da BARBARA CAMPINA ALVES 70448996413 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 10 Melhores Barbearias em Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3178,29 +3206,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a BARBARA CAMPINA ALVES 70448996413?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 10 Melhores Barbearias em Campinas?</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://wa.me/55704489964100?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20BARBARA%20CAMPINA%20ALVES%2070448996413%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551932941717?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2010%20Melhores%20Barbearias%20em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://wa.me/55704489964100?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20BARBARA%20CAMPINA%20ALVES%2070448996413%3F</t>
+          <t>https://wa.me/551932941717?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2010%20Melhores%20Barbearias%20em%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Yahoo Search</t>
+          <t>Encontrar seu smartphone</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yahoo Search – Busca na Web</t>
+          <t>Encontrar seu smartphone</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3215,34 +3243,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O mecanismo de busca que ajuda a localizar exatamente o que você procura. Busque as informações, víd...</t>
+          <t>Configurações da Conta do Google. Ajuda. Fazer login....</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://br.search.yahoo.com/?fr2=p:fprd,mkt:br</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CA) 98877-6655</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Yahoo%20Search%20campinas</t>
+          <t>https://www.google.com/maps/search/Encontrar%20seu%20smartphone%20campinas</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Yahoo Search aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Encontrar seu smartphone aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3252,17 +3280,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Yahoo Search?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Encontrar seu smartphone?</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Yahoo%20Search%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Encontrar%20seu%20smartphone%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Yahoo%20Search%20campinas%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Encontrar%20seu%20smartphone%3F</t>
         </is>
       </c>
     </row>

--- a/leads_dentista_campinas.xlsx
+++ b/leads_dentista_campinas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,12 +639,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clnica Odontolgica Odonthos Odontologia Campi</t>
+          <t>Sculpere Clnica Odontolgica</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clínica Odontológica Odonthos Odontologia Campinas</t>
+          <t>Sculpere Clínica Odontológica - Campinas - SP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dentista Campinas. Odonthos odontologia integrada crosp: 17.203. Cirurgiões dentistas atuando em vár...</t>
+          <t>Referência em Clínica Odontológica em Campinas. Dentistas Especializados em Implantes, Próteses e Es...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -669,24 +669,28 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.odonthos.com.br/</t>
+          <t>https://sculpere.com.br/</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>19982555</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5519982555</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Odontolgica%20Odonthos%20Odontologia%20Campi%20campinas</t>
+          <t>https://www.google.com/maps/search/Sculpere%20Clnica%20Odontolgica%20campinas</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Odontolgica Odonthos Odontologia Campi aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Sculpere Clnica Odontolgica aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -696,17 +700,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Odontolgica Odonthos Odontologia Campi?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Sculpere Clnica Odontolgica?</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Odontolgica%20Odonthos%20Odontologia%20Campi%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519982555?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Sculpere%20Clnica%20Odontolgica%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Odontolgica%20Odonthos%20Odontologia%20Campi%3F</t>
+          <t>https://wa.me/5519982555?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Sculpere%20Clnica%20Odontolgica%3F</t>
         </is>
       </c>
     </row>
@@ -787,12 +791,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dentistas em Centro, Campinas</t>
+          <t>Dentista e Odontologia Especializada em Campi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dentistas em Centro, Campinas - SP | DentMap</t>
+          <t>Dentista e Odontologia Especializada em Campinas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -807,7 +811,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Encontre dentistas em Centro, Campinas. Compare avaliacoes, especialidades e agende sua consulta no ...</t>
+          <t>Em 2011, após todo um processo de seleção de cidades e locais, foi construída dentro das mais novas ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -817,28 +821,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://dentmap.com.br/dentistas/campinas?especialidade=clinico-geral&amp;bairro=Centro&amp;pagina=5</t>
+          <t>https://greghiodontologia.com.br/</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(19) 3326-1410</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>551933261410</t>
-        </is>
-      </c>
+          <t>(CA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentistas%20em%20Centro%2C%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentista%20e%20Odontologia%20Especializada%20em%20Campi%20campinas</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentistas em Centro, Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentista e Odontologia Especializada em Campi aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -848,29 +848,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentistas em Centro, Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista e Odontologia Especializada em Campi?</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://wa.me/551933261410?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentistas%20em%20Centro%2C%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20e%20Odontologia%20Especializada%20em%20Campi%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://wa.me/551933261410?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentistas%20em%20Centro%2C%20Campinas%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%20e%20Odontologia%20Especializada%20em%20Campi%3F</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dentista e Odontologia Especializada em Campi</t>
+          <t>Dentista 24 Horas Campinas (19) 9 9409-5553</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dentista e Odontologia Especializada em Campinas</t>
+          <t>Dentista 24 Horas Campinas (19) 9 9409-5553 Whatsapp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Em 2011, após todo um processo de seleção de cidades e locais, foi construída dentro das mais novas ...</t>
+          <t>logo dentista 24horas campinas. Rua Jerônimo Páttaro 364 – Barão Geraldo – Campinas SP.Chamar no Wha...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://greghiodontologia.com.br/</t>
+          <t>https://dentista24horascampinas.com.br/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -906,13 +906,13 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentista%20e%20Odontologia%20Especializada%20em%20Campi%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%20campinas</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentista e Odontologia Especializada em Campi aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentista 24 Horas Campinas (19) 9 9409-5553 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -922,29 +922,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentista e Odontologia Especializada em Campi?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista 24 Horas Campinas (19) 9 9409-5553?</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20e%20Odontologia%20Especializada%20em%20Campi%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%20e%20Odontologia%20Especializada%20em%20Campi%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%3F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10 melhores dentistas para Campinas</t>
+          <t>Clnica Odontolgica Odonthos Odontologia Campi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10 melhores dentistas para Campinas</t>
+          <t>Clínica Odontológica Odonthos Odontologia Campinas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nossos melhores dentistas em Campinas, avaliados pela comunidade StarOfService - Campinas, São Paulo...</t>
+          <t>Dentista Campinas. Odonthos odontologia integrada crosp: 17.203. Cirurgiões dentistas atuando em vár...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -969,28 +969,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.starofservice.com.br/dir/sao-paulo/campinas/campinas/servicos-dentarios</t>
+          <t>https://www.odonthos.com.br/</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(19) 97419-5901</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5519974195901</t>
-        </is>
-      </c>
+          <t>(CA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/10%20melhores%20dentistas%20para%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Clnica%20Odontolgica%20Odonthos%20Odontologia%20Campi%20campinas</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 10 melhores dentistas para Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica Odontolgica Odonthos Odontologia Campi aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1000,29 +996,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 10 melhores dentistas para Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Odontolgica Odonthos Odontologia Campi?</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://wa.me/5519974195901?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2010%20melhores%20dentistas%20para%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Odontolgica%20Odonthos%20Odontologia%20Campi%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://wa.me/5519974195901?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2010%20melhores%20dentistas%20para%20Campinas%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Odontolgica%20Odonthos%20Odontologia%20Campi%3F</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dentista 24 Horas Campinas (19) 9 9409-5553</t>
+          <t>Ana Carolina Diniz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dentista 24 Horas Campinas (19) 9 9409-5553 Whatsapp</t>
+          <t>Ana Carolina Diniz - Dentista Campinas - SP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1037,7 +1033,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>logo dentista 24horas campinas. Rua Jerônimo Páttaro 364 – Barão Geraldo – Campinas SP.Chamar no Wha...</t>
+          <t>Ana Carolina é Cirurgiã-Dentista com graduação em Odontologia e pós-graduação em Implantodontia. Apa...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1047,24 +1043,28 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://dentista24horascampinas.com.br/</t>
+          <t>https://www.anacarolinadiniz.com/</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(19) 98332-9496</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5519983329496</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%20campinas</t>
+          <t>https://www.google.com/maps/search/Ana%20Carolina%20Diniz%20campinas</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentista 24 Horas Campinas (19) 9 9409-5553 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Ana Carolina Diniz aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1074,29 +1074,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentista 24 Horas Campinas (19) 9 9409-5553?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Ana Carolina Diniz?</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519983329496?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Ana%20Carolina%20Diniz%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%2024%20Horas%20Campinas%20%2819%29%209%209409-5553%3F</t>
+          <t>https://wa.me/5519983329496?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Ana%20Carolina%20Diniz%3F</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Os Melhores Dentistas em Campinas, SP</t>
+          <t>Odontologia Vetorasso</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Os Melhores Dentistas em Campinas, SP — WhatsApp</t>
+          <t>Odontologia Vetorasso | dentista campinas | Rua Barata Ribeiro, 5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Veja os dentistas mais bem avaliados em Campinas, SP. Clareamento, implantes, ortodontia, limpeza, r...</t>
+          <t>Dentista em Campinas, Odontologia Vetorasso, há mais de 40 anos cuidando do seu sorriso.Bem-vindo ao...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.odontologiavetorasso.com/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1132,13 +1132,13 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Os%20Melhores%20Dentistas%20em%20Campinas%2C%20SP%20campinas</t>
+          <t>https://www.google.com/maps/search/Odontologia%20Vetorasso%20campinas</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Os Melhores Dentistas em Campinas, SP aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Odontologia Vetorasso aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1148,29 +1148,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Os Melhores Dentistas em Campinas, SP?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odontologia Vetorasso?</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Os%20Melhores%20Dentistas%20em%20Campinas%2C%20SP%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20Vetorasso%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Os%20Melhores%20Dentistas%20em%20Campinas%2C%20SP%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%20Vetorasso%3F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dra Camila Roberta</t>
+          <t>Odontoclinic Campinas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dra Camila Roberta - Odontologia | Campinas SP - FacebookConsultó</t>
+          <t>Odontoclinic Campinas - Dentista no Campo Grande</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1185,34 +1185,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Realizamos a gengivoplastia, ajustando o contorno da gengiva, e finalizamos com o clareamento dental...</t>
+          <t>A clínica mais procurada da região de Campo Grande - Campinas - pelo atendimento de qualidade do tra...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://dentistanocampogrande.com.br/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(19) 97122-6504</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5519971226504</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dra%20Camila%20Roberta%20campinas</t>
+          <t>https://www.google.com/maps/search/Odontoclinic%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dra Camila Roberta aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Odontoclinic Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1222,29 +1226,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dra Camila Roberta?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odontoclinic Campinas?</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dra%20Camila%20Roberta%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519971226504?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontoclinic%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dra%20Camila%20Roberta%3F</t>
+          <t>https://wa.me/5519971226504?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontoclinic%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Consultrio Dentrio 24 Horas Campinas (19) 9 9</t>
+          <t>Odontologia Campinas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Consultório Dentário 24 Horas Campinas (19) 9 9409-5553 Whatsapp</t>
+          <t>Odontologia Campinas | Artesania | Studio Oral Campinas | Brasil</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1259,7 +1263,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Consultório Dentário 24 Horas Campinas (19) 9 9409-5553 Whatsapp Consultório Dentário 24 Horas Campi...</t>
+          <t>restauracao e proteses dentista campinas. Restaurações. e Próteses. bruxismo dental em campinas.png....</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1269,28 +1273,28 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://dentista24horascampinas.com.br/consultorio-dentario-24-horas-campinas/</t>
+          <t>https://www.artesaniaoral.com/</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(19) 99409-5553</t>
+          <t>(19) 3242-4670</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5519994095553</t>
+          <t>551932424670</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Consultrio%20Dentrio%2024%20Horas%20Campinas%20%2819%29%209%209%20campinas</t>
+          <t>https://www.google.com/maps/search/Odontologia%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Consultrio Dentrio 24 Horas Campinas (19) 9 9 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Odontologia Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1300,29 +1304,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Consultrio Dentrio 24 Horas Campinas (19) 9 9?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odontologia Campinas?</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://wa.me/5519994095553?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consultrio%20Dentrio%2024%20Horas%20Campinas%20%2819%29%209%209%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551932424670?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://wa.me/5519994095553?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consultrio%20Dentrio%2024%20Horas%20Campinas%20%2819%29%209%209%3F</t>
+          <t>https://wa.me/551932424670?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ana Carolina Diniz</t>
+          <t>Dentistas em Centro, Campinas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ana Carolina Diniz - Dentista Campinas - SP</t>
+          <t>Dentistas em Centro, Campinas - SP | DentMap</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1337,7 +1341,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ana Carolina é Cirurgiã-Dentista com graduação em Odontologia e pós-graduação em Implantodontia. Apa...</t>
+          <t>Encontre os melhores dentistas em Centro, Campinas. Compare avaliações, especialidades e agende sua ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1347,28 +1351,28 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.anacarolinadiniz.com/</t>
+          <t>https://dentmap.com.br/dentistas/campinas/centro</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(19) 98332-9496</t>
+          <t>(19) 3326-1410</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5519983329496</t>
+          <t>551933261410</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Ana%20Carolina%20Diniz%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentistas%20em%20Centro%2C%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Ana Carolina Diniz aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentistas em Centro, Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1378,29 +1382,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Ana Carolina Diniz?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentistas em Centro, Campinas?</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://wa.me/5519983329496?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Ana%20Carolina%20Diniz%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551933261410?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentistas%20em%20Centro%2C%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://wa.me/5519983329496?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Ana%20Carolina%20Diniz%3F</t>
+          <t>https://wa.me/551933261410?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentistas%20em%20Centro%2C%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Odontologia Vetorasso</t>
+          <t>Os Melhores Dentistas em Campinas, SP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Odontologia Vetorasso | dentista campinas | Rua Barata Ribeiro, 5</t>
+          <t>Os Melhores Dentistas em Campinas, SP — WhatsApp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1415,17 +1419,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dentista em Campinas, Odontologia Vetorasso, há mais de 40 anos cuidando do seu sorriso.Bem-vindo ao...</t>
+          <t>Veja os dentistas mais bem avaliados em Campinas, SP. Clareamento, implantes, ortodontia, limpeza, r...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.odontologiavetorasso.com/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1436,13 +1440,13 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Odontologia%20Vetorasso%20campinas</t>
+          <t>https://www.google.com/maps/search/Os%20Melhores%20Dentistas%20em%20Campinas%2C%20SP%20campinas</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odontologia Vetorasso aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Os Melhores Dentistas em Campinas, SP aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1452,29 +1456,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odontologia Vetorasso?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Os Melhores Dentistas em Campinas, SP?</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20Vetorasso%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Os%20Melhores%20Dentistas%20em%20Campinas%2C%20SP%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%20Vetorasso%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Os%20Melhores%20Dentistas%20em%20Campinas%2C%20SP%3F</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Odontoclinic Campinas</t>
+          <t>Consultrio Dentrio 24 Horas Campinas (19) 9 9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Odontoclinic Campinas - Dentista no Campo Grande</t>
+          <t>Consultório Dentário 24 Horas Campinas (19) 9 9409-5553 Whatsapp</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1489,7 +1493,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A clínica mais procurada da região de Campo Grande - Campinas - pelo atendimento de qualidade do tra...</t>
+          <t>Consultório Dentário 24 Horas Campinas (19) 9 9409-5553 Whatsapp Consultório Dentário 24 Horas Campi...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1499,24 +1503,28 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://dentistanocampogrande.com.br/</t>
+          <t>https://dentista24horascampinas.com.br/consultorio-dentario-24-horas-campinas/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(19) 99409-5553</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5519994095553</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Odontoclinic%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Consultrio%20Dentrio%2024%20Horas%20Campinas%20%2819%29%209%209%20campinas</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odontoclinic Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Consultrio Dentrio 24 Horas Campinas (19) 9 9 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1526,29 +1534,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odontoclinic Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Consultrio Dentrio 24 Horas Campinas (19) 9 9?</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontoclinic%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519994095553?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consultrio%20Dentrio%2024%20Horas%20Campinas%20%2819%29%209%209%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontoclinic%20Campinas%3F</t>
+          <t>https://wa.me/5519994095553?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consultrio%20Dentrio%2024%20Horas%20Campinas%20%2819%29%209%209%3F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sculpere Clnica Odontolgica</t>
+          <t>Implante Dentrio em Campinas SP (19) 99998-45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sculpere Clínica Odontológica - Campinas - SP</t>
+          <t>Implante Dentário em Campinas SP (19) 99998-4516 Whatsapp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1563,7 +1571,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dentista Campinas. Home. Clínica.Acreditamos que o resultado de um tratamento é altamente dependente...</t>
+          <t>Periodontia e prevenção – Saúde bucal em primeiro lugar Atendemos Campinas e região! Nosso consultór...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1573,28 +1581,28 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://sculpere.com.br/</t>
+          <t>https://dentistacampinas.odo.br/</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19982555</t>
+          <t>(19) 99998-4516</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5519982555</t>
+          <t>5519999984516</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Sculpere%20Clnica%20Odontolgica%20campinas</t>
+          <t>https://www.google.com/maps/search/Implante%20Dentrio%20em%20Campinas%20SP%20%2819%29%2099998-45%20campinas</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Sculpere Clnica Odontolgica aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Implante Dentrio em Campinas SP (19) 99998-45 aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1604,29 +1612,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Sculpere Clnica Odontolgica?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Implante Dentrio em Campinas SP (19) 99998-45?</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://wa.me/5519982555?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Sculpere%20Clnica%20Odontolgica%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519999984516?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Implante%20Dentrio%20em%20Campinas%20SP%20%2819%29%2099998-45%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://wa.me/5519982555?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Sculpere%20Clnica%20Odontolgica%3F</t>
+          <t>https://wa.me/5519999984516?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Implante%20Dentrio%20em%20Campinas%20SP%20%2819%29%2099998-45%3F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Odontologia Campinas</t>
+          <t>Campinas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Odontologia Campinas | Artesania | Studio Oral Campinas | Brasil</t>
+          <t>Campinas – Guanabara - Odontoclinic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1641,7 +1649,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>restauracao e proteses dentista campinas. Restaurações. e Próteses. bruxismo dental em campinas.png....</t>
+          <t>Esse é o nosso compromisso com você: dentistas altamente qualificados, inovação e tecnologia nos tra...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1651,28 +1659,28 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.artesaniaoral.com/</t>
+          <t>https://odontoclinic.com.br/unidades/campinas-guanabara/</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(19) 3242-4670</t>
+          <t>(19) 2116-0555</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>551932424670</t>
+          <t>551921160555</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Odontologia%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Campinas%20campinas</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odontologia Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1682,29 +1690,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odontologia Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Campinas?</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://wa.me/551932424670?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551921160555?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://wa.me/551932424670?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%20Campinas%3F</t>
+          <t>https://wa.me/551921160555?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Clnica Odontolgica Em Campinas</t>
+          <t>Clnica Synergia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Clínica Odontológica Em Campinas | Intégra Odontologia E Saúde</t>
+          <t>Clínica Synergia – Cuidados Odontológicos</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1719,7 +1727,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Não se preocupe, aqui na Intégra Odontologia e Saúde, você será atendido pelos melhores dentistas de...</t>
+          <t>Agende via WhatsApp. Na Clínica Synergia, cada detalhe é pensado para proporcionar tratamentos perso...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1729,28 +1737,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.integraodontosaude.com.br/</t>
+          <t>https://clinicasynergia.com.br/</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(19) 3326-1406</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>551933261406</t>
-        </is>
-      </c>
+          <t>(CA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Odontolgica%20Em%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Clnica%20Synergia%20campinas</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Odontolgica Em Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica Synergia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1760,17 +1764,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Odontolgica Em Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Synergia?</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://wa.me/551933261406?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Odontolgica%20Em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Synergia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://wa.me/551933261406?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Odontolgica%20Em%20Campinas%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Synergia%3F</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1859,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Clnica Synergia</t>
+          <t>10 melhores dentistas para Campinas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Clínica Synergia – Cuidados Odontológicos</t>
+          <t>10 melhores dentistas para Campinas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1875,7 +1879,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Agende via WhatsApp. Na Clínica Synergia, cada detalhe é pensado para proporcionar tratamentos perso...</t>
+          <t>Dentista. 13023-490 Campinas. A clinica integra vários dentistas, e cada um cuida de uma especialida...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1885,28 +1889,28 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://clinicasynergia.com.br/</t>
+          <t>https://www.starofservice.com.br/dir/sao-paulo/campinas/campinas/servicos-dentarios</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19323129</t>
+          <t>(19) 97419-5901</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5519323129</t>
+          <t>5519974195901</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Synergia%20campinas</t>
+          <t>https://www.google.com/maps/search/10%20melhores%20dentistas%20para%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Synergia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 10 melhores dentistas para Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1916,29 +1920,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Synergia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 10 melhores dentistas para Campinas?</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://wa.me/5519323129?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Synergia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519974195901?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2010%20melhores%20dentistas%20para%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://wa.me/5519323129?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Synergia%3F</t>
+          <t>https://wa.me/5519974195901?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2010%20melhores%20dentistas%20para%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>Dentista</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>Dentista | Campinas | Intégra Odontologia &amp; Saúde</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1953,34 +1957,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>The site owner hides the web page description....</t>
+          <t>Dentistas Mestre e Especialistas para cuidar de você com dedicação e carinho. A Intégra Odontologia ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.integraodontosaude.com.br/dentista</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(19) 3383-9362</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>551933839362</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Link%20to%20instagram.com%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentista%20campinas</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to instagram.com aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Dentista aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1990,17 +1998,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to instagram.com?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista?</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20instagram.com%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551933839362?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20instagram.com%3F</t>
+          <t>https://wa.me/551933839362?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%3F</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2089,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Clnica Dentista Campinas</t>
+          <t>Clnica Odontolgica Smile Center Campinas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Clínica Dentista Campinas - Imcamp</t>
+          <t>Clínica Odontológica Smile Center Campinas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2101,7 +2109,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Clínica Dentista Campinas. Normalmente ao pensar em dentistas em Campinas, as pessoas imaginem um pr...</t>
+          <t>A clínica odontológica Smile Center Campinas tem como objetivo o atendimento multidisciplinar, integ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2111,24 +2119,28 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://imcamp.com.br/service/clinica-dentista-campinas/</t>
+          <t>https://smilecampinas.com.br/</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(19) 3241-1840</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>551932411840</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Dentista%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Clnica%20Odontolgica%20Smile%20Center%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Dentista Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica Odontolgica Smile Center Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2138,29 +2150,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Dentista Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Odontolgica Smile Center Campinas?</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Dentista%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551932411840?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Odontolgica%20Smile%20Center%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Dentista%20Campinas%3F</t>
+          <t>https://wa.me/551932411840?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Odontolgica%20Smile%20Center%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clnica Odontolgica Smile Center Campinas</t>
+          <t>OdontoCampinas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Clínica Odontológica Smile Center Campinas</t>
+          <t>OdontoCampinas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2175,7 +2187,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>A clínica odontológica Smile Center Campinas tem como objetivo o atendimento multidisciplinar, integ...</t>
+          <t>Com mais de 10 anos de experiência e mais de 1000 sorrisos atendidos, somos sua escolha confiável pa...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2185,28 +2197,28 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://smilecampinas.com.br/</t>
+          <t>http://www.odontocampinas.com.br/</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(19) 3241-1840</t>
+          <t>(19) 98765-7174</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>551932411840</t>
+          <t>5519987657174</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Odontolgica%20Smile%20Center%20Campinas%20campinas</t>
+          <t>https://www.google.com/maps/search/OdontoCampinas%20campinas</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Odontolgica Smile Center Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da OdontoCampinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2216,29 +2228,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Odontolgica Smile Center Campinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a OdontoCampinas?</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://wa.me/551932411840?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Odontolgica%20Smile%20Center%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519987657174?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OdontoCampinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://wa.me/551932411840?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Odontolgica%20Smile%20Center%20Campinas%3F</t>
+          <t>https://wa.me/5519987657174?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OdontoCampinas%3F</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OdontoCampinas</t>
+          <t>Dentistas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OdontoCampinas</t>
+          <t>Dentistas | Implantes Protocolo | Ortodontia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2253,7 +2265,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Com mais de 10 anos de experiência e mais de 1000 sorrisos atendidos, somos sua escolha confiável pa...</t>
+          <t>Clínica Sorriso de Campinas – Qualidade que cabe no seu bolso! Implantes, próteses, aparelhos e muit...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2263,28 +2275,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>http://www.odontocampinas.com.br/</t>
+          <t>https://www.sorrisodecampinas.com/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(19) 98765-7174</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5519987657174</t>
-        </is>
-      </c>
+          <t>(CA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/OdontoCampinas%20campinas</t>
+          <t>https://www.google.com/maps/search/Dentistas%20campinas</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da OdontoCampinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentistas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2294,29 +2302,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a OdontoCampinas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentistas?</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://wa.me/5519987657174?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OdontoCampinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentistas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://wa.me/5519987657174?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OdontoCampinas%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentistas%3F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dentistas</t>
+          <t>Oral Unic</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dentistas | Implantes Protocolo | Ortodontia</t>
+          <t>Oral Unic - Campinas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2331,7 +2339,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Clínica Sorriso de Campinas – Qualidade que cabe no seu bolso! Implantes, próteses, aparelhos e muit...</t>
+          <t>Fale Conosco Nosso (s) telefone (s) (19) 9 9947-3093 Nosso e-mail administrativo@oraluniccampinas.co...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,24 +2349,28 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.sorrisodecampinas.com/</t>
+          <t>https://www.oralunic.com.br/campinas-sp</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(19) 99974-4496</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5519999744496</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentistas%20campinas</t>
+          <t>https://www.google.com/maps/search/Oral%20Unic%20campinas</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentistas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Oral Unic aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2368,29 +2380,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentistas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Oral Unic?</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentistas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519999744496?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Oral%20Unic%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentistas%3F</t>
+          <t>https://wa.me/5519999744496?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Oral%20Unic%3F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Principal</t>
+          <t>Rhema Clnica Odontologia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Principal - Clínica Zerbinatti</t>
+          <t>Rhema Clínica Odontologia | Dentista em Campinas | Av Ten ...</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2405,7 +2417,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Depois de anos buscando um diagnóstico, finalmente pude encontrar um profissional com um olhar clíni...</t>
+          <t>Entre em contato conosco hoje mesmo para agendar uma consulta e experimentar a diferença que nossa c...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2415,28 +2427,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://clinicazerbinatti.com.br/</t>
+          <t>https://www.rhemaclinica.com/</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(19) 3045-9140</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>551930459140</t>
-        </is>
-      </c>
+          <t>(CA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Principal%20campinas</t>
+          <t>https://www.google.com/maps/search/Rhema%20Clnica%20Odontologia%20campinas</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Principal aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Rhema Clnica Odontologia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2446,17 +2454,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Principal?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Rhema Clnica Odontologia?</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://wa.me/551930459140?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Principal%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Rhema%20Clnica%20Odontologia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://wa.me/551930459140?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Principal%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Rhema%20Clnica%20Odontologia%3F</t>
         </is>
       </c>
     </row>
@@ -2498,10 +2506,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(19) 98242-4662</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5519982424662</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Dentista%20em%20Campinas%20campinas</t>
@@ -2525,12 +2537,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519982424662?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%20em%20Campinas%3F</t>
+          <t>https://wa.me/5519982424662?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%20em%20Campinas%3F</t>
         </is>
       </c>
     </row>
@@ -2572,12 +2584,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(11) 3089-6060</t>
+          <t>(19) 4560-3770</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>551130896060</t>
+          <t>551945603770</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2603,24 +2615,24 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://wa.me/551130896060?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%2024%20Horas%20em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551945603770?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%2024%20Horas%20em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://wa.me/551130896060?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%2024%20Horas%20em%20Campinas%3F</t>
+          <t>https://wa.me/551945603770?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%2024%20Horas%20em%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Emergncia Odontolgica em Campinas 24h</t>
+          <t>Clnica Dentista Campinas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Emergência Odontológica em Campinas 24h | Dra. Silvia Satriuc</t>
+          <t>Clínica Dentista Campinas - Imcamp</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2635,7 +2647,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dentista em Campinas. Emergência Odontológica Plantão das 7hs as 23hs.Melhorias estéticas no sorriso...</t>
+          <t>A clínica dentista Campinas é um centro atendimento onde vários dentistas especialistas trabalham em...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2645,24 +2657,28 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://silviasatriuc.com.br/</t>
+          <t>https://imcamp.com.br/service/clinica-dentista-campinas/</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(19) 3232-2555</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>551932322555</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Emergncia%20Odontolgica%20em%20Campinas%2024h%20campinas</t>
+          <t>https://www.google.com/maps/search/Clnica%20Dentista%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Emergncia Odontolgica em Campinas 24h aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica Dentista Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2672,29 +2688,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Emergncia Odontolgica em Campinas 24h?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Dentista Campinas?</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Emergncia%20Odontolgica%20em%20Campinas%2024h%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551932322555?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Dentista%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Emergncia%20Odontolgica%20em%20Campinas%2024h%3F</t>
+          <t>https://wa.me/551932322555?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Dentista%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dra. Anita Monteiro</t>
+          <t>A Barbearia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dra. Anita Monteiro - Dentista Campinas, odontologia e mais</t>
+          <t>A Barbearia – A melhor barbearia da Campinas!</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2709,7 +2725,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Um atendimento acolhedor, cheio de profissionalismo e cuidado, moro em Indaiatuba e faço questão de ...</t>
+          <t>A Barbearia – A melhor barbearia da Campinas!...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2719,24 +2735,28 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://odontologiamonteiro.com.br/</t>
+          <t>https://www.abarbearia.net/</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(57) 3711-2900</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>555737112900</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dra.%20Anita%20Monteiro%20campinas</t>
+          <t>https://www.google.com/maps/search/A%20Barbearia%20campinas</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dra. Anita Monteiro aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da A Barbearia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2746,29 +2766,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dra. Anita Monteiro?</t>
+Posso te mandar a prévia demonstrativa que fiz para a A Barbearia?</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dra.%20Anita%20Monteiro%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/555737112900?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20A%20Barbearia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dra.%20Anita%20Monteiro%3F</t>
+          <t>https://wa.me/555737112900?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20A%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dentista</t>
+          <t>Penny Lane Barbearia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dentista | Campinas | Intégra Odontologia &amp; Saúde</t>
+          <t>Penny Lane Barbearia | Barbearia Premium em Campinas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2783,17 +2803,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dentistas Mestre e Especialistas para cuidar de você com dedicação e carinho. A Intégra Odontologia ...</t>
+          <t>Corte masculino, barba, prótese capilar, visagismo e atendimento VIP para noivos. A barbearia referê...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.integraodontosaude.com.br/dentista</t>
+          <t>https://www.pennylanebarbearia.com.br/</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2804,13 +2824,13 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentista%20campinas</t>
+          <t>https://www.google.com/maps/search/Penny%20Lane%20Barbearia%20campinas</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentista aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Penny Lane Barbearia aí em Campinas no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2820,29 +2840,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentista?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Penny Lane Barbearia?</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Penny%20Lane%20Barbearia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Penny%20Lane%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rhema Clnica Odontologia</t>
+          <t>Barbearia Campinas Centro</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rhema Clínica Odontologia | Dentista em Campinas | Av Ten ...</t>
+          <t>Barbearia Campinas Centro - Campinas - SP - Guiamapa.com</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2857,7 +2877,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Entre em contato conosco hoje mesmo para agendar uma consulta e experimentar a diferença que nossa c...</t>
+          <t>Veja onde fica e como chegar em Barbearia Campinas utilizando nosso mapa e confira informações adici...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2867,28 +2887,28 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.rhemaclinica.com/</t>
+          <t>https://guiamapa.com/onde-fica/barbearia-campinas/campinas/sp/92911</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>19324150</t>
+          <t>(19) 98604-9825</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5519324150</t>
+          <t>5519986049825</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Rhema%20Clnica%20Odontologia%20campinas</t>
+          <t>https://www.google.com/maps/search/Barbearia%20Campinas%20Centro%20campinas</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Rhema Clnica Odontologia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia Campinas Centro aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2898,29 +2918,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Rhema Clnica Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Campinas Centro?</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://wa.me/5519324150?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Rhema%20Clnica%20Odontologia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519986049825?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Campinas%20Centro%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://wa.me/5519324150?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Rhema%20Clnica%20Odontologia%3F</t>
+          <t>https://wa.me/5519986049825?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Campinas%20Centro%3F</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A Barbearia</t>
+          <t>10 Melhores Barbearias em Campinas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A Barbearia – A melhor barbearia da Campinas!</t>
+          <t>10 Melhores Barbearias em Campinas — Guia 2026 | Beard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2935,7 +2955,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>A Barbearia – A melhor barbearia da Campinas!...</t>
+          <t>Se você está em busca de um bom barbeiro em Campinas, este guia reúne as 10 melhores opções avaliada...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2945,28 +2965,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.abarbearia.net/</t>
+          <t>https://blog.beard.com.br/barbearias-em-campinas/</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(19) 98990-7633</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5519989907633</t>
-        </is>
-      </c>
+          <t>(CA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/A%20Barbearia%20campinas</t>
+          <t>https://www.google.com/maps/search/10%20Melhores%20Barbearias%20em%20Campinas%20campinas</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da A Barbearia aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 10 Melhores Barbearias em Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2976,29 +2992,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a A Barbearia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 10 Melhores Barbearias em Campinas?</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://wa.me/5519989907633?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20A%20Barbearia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2010%20Melhores%20Barbearias%20em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://wa.me/5519989907633?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20A%20Barbearia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2010%20Melhores%20Barbearias%20em%20Campinas%3F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Penny Lane Barbearia</t>
+          <t>Encontrar seu smartphone</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Penny Lane Barbearia | Barbearia Premium em Campinas</t>
+          <t>Encontrar seu smartphone</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3013,17 +3029,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Corte masculino, barba, prótese capilar, visagismo e atendimento VIP para noivos. A barbearia referê...</t>
+          <t>Configurações da Conta do Google. Ajuda. Fazer login....</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.pennylanebarbearia.com.br/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3034,13 +3050,13 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Penny%20Lane%20Barbearia%20campinas</t>
+          <t>https://www.google.com/maps/search/Encontrar%20seu%20smartphone%20campinas</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Penny Lane Barbearia aí em Campinas no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da Encontrar seu smartphone aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3050,245 +3066,15 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Penny Lane Barbearia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Encontrar seu smartphone?</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Penny%20Lane%20Barbearia%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Encontrar%20seu%20smartphone%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Penny%20Lane%20Barbearia%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Barbearia Campinas Centro</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Barbearia Campinas Centro - Campinas - SP - Guiamapa.com</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Campinas</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Veja onde fica e como chegar em Barbearia Campinas utilizando nosso mapa e confira informações adici...</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://guiamapa.com/onde-fica/barbearia-campinas/campinas/sp/92911</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(19) 98604-9825</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5519986049825</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Barbearia%20Campinas%20Centro%20campinas</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia Campinas Centro aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia Campinas Centro?</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>https://wa.me/5519986049825?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Campinas%20Centro%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>https://wa.me/5519986049825?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Campinas%20Centro%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>10 Melhores Barbearias em Campinas</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>10 Melhores Barbearias em Campinas — Guia 2026 | Beard</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Campinas</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Se você está em busca de um bom barbeiro em Campinas, este guia reúne as 10 melhores opções avaliada...</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://blog.beard.com.br/barbearias-em-campinas/</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(19) 3294-1717</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>551932941717</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/10%20Melhores%20Barbearias%20em%20Campinas%20campinas</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 10 Melhores Barbearias em Campinas aí em Campinas no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 10 Melhores Barbearias em Campinas?</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>https://wa.me/551932941717?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2010%20Melhores%20Barbearias%20em%20Campinas%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>https://wa.me/551932941717?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2010%20Melhores%20Barbearias%20em%20Campinas%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Encontrar seu smartphone</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Encontrar seu smartphone</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Campinas</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Configurações da Conta do Google. Ajuda. Fazer login....</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Sem Site Cadastrado</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(CA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Encontrar%20seu%20smartphone%20campinas</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Encontrar seu smartphone aí em Campinas no Google e vi que vocês ainda não têm um site próprio para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Encontrar seu smartphone?</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Encontrar%20seu%20smartphone%20a%C3%AD%20em%20Campinas%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
         <is>
           <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Encontrar%20seu%20smartphone%3F</t>
         </is>

--- a/leads_dentista_campinas.xlsx
+++ b/leads_dentista_campinas.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dentistas em Campinas</t>
+          <t>Dentistas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dra. Lvia Sousa, Dentista, R. Tiradentes, 446</t>
+          <t>Dra. Lvia Sousa, Dentista, R. Tiradentes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -677,10 +677,8 @@
           <t>19982555</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5519982555</t>
-        </is>
+      <c r="I4" t="n">
+        <v>5519982555</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -717,7 +715,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Especialista em Implantes Dentrios em Campina</t>
+          <t>Especialista em Implantes Dentrios em Ca</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -791,7 +789,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dentista e Odontologia Especializada em Campi</t>
+          <t>Dentista e Odontologia Especializada em</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -865,7 +863,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dentista 24 Horas Campinas (19) 9 9409-5553</t>
+          <t>Dentista 24 Horas Campinas (19) 9 9409-5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -939,7 +937,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Clnica Odontolgica Odonthos Odontologia Campi</t>
+          <t>Clnica Odontolgica Odonthos Odontologia</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1051,10 +1049,8 @@
           <t>(19) 98332-9496</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5519983329496</t>
-        </is>
+      <c r="I9" t="n">
+        <v>5519983329496</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1165,7 +1161,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Odontoclinic Campinas</t>
+          <t>Odontoclinic</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1203,10 +1199,8 @@
           <t>(19) 97122-6504</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5519971226504</t>
-        </is>
+      <c r="I11" t="n">
+        <v>5519971226504</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1243,7 +1237,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Odontologia Campinas</t>
+          <t>Odontologia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1281,10 +1275,8 @@
           <t>(19) 3242-4670</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>551932424670</t>
-        </is>
+      <c r="I12" t="n">
+        <v>551932424670</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1321,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dentistas em Centro, Campinas</t>
+          <t>Dentistas em Centro</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1359,10 +1351,8 @@
           <t>(19) 3326-1410</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>551933261410</t>
-        </is>
+      <c r="I13" t="n">
+        <v>551933261410</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1399,7 +1389,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Os Melhores Dentistas em Campinas, SP</t>
+          <t>Os Melhores Dentistas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1473,7 +1463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Consultrio Dentrio 24 Horas Campinas (19) 9 9</t>
+          <t>Consultrio Dentrio 24 Horas Campinas (19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1511,10 +1501,8 @@
           <t>(19) 99409-5553</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5519994095553</t>
-        </is>
+      <c r="I15" t="n">
+        <v>5519994095553</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1551,7 +1539,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Implante Dentrio em Campinas SP (19) 99998-45</t>
+          <t>Implante Dentrio em Campinas Sp (19) 999</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1589,10 +1577,8 @@
           <t>(19) 99998-4516</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5519999984516</t>
-        </is>
+      <c r="I16" t="n">
+        <v>5519999984516</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1667,10 +1653,8 @@
           <t>(19) 2116-0555</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>551921160555</t>
-        </is>
+      <c r="I17" t="n">
+        <v>551921160555</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1781,7 +1765,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Consultrio Odontolgico Mariana Szatkovski 5.0</t>
+          <t>Consultrio Odontolgico Mariana Szatkovsk</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1819,10 +1803,8 @@
           <t>(19) 2116-0156</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>551921160156</t>
-        </is>
+      <c r="I19" t="n">
+        <v>551921160156</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1859,14 +1841,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>10 Melhores Dentistas para</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>10 melhores dentistas para Campinas</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>10 melhores dentistas para Campinas</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>Campinas</t>
@@ -1897,10 +1879,8 @@
           <t>(19) 97419-5901</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5519974195901</t>
-        </is>
+      <c r="I20" t="n">
+        <v>5519974195901</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1975,10 +1955,8 @@
           <t>(19) 3383-9362</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>551933839362</t>
-        </is>
+      <c r="I21" t="n">
+        <v>551933839362</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2015,7 +1993,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Procure seu Dentista</t>
+          <t>Procure Seu Dentista</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2089,7 +2067,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Clnica Odontolgica Smile Center Campinas</t>
+          <t>Clnica Odontolgica Smile Center</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2127,10 +2105,8 @@
           <t>(19) 3241-1840</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>551932411840</t>
-        </is>
+      <c r="I23" t="n">
+        <v>551932411840</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2167,14 +2143,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Odontocampinas</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>OdontoCampinas</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>OdontoCampinas</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>Campinas</t>
@@ -2205,10 +2181,8 @@
           <t>(19) 98765-7174</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5519987657174</t>
-        </is>
+      <c r="I24" t="n">
+        <v>5519987657174</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2357,10 +2331,8 @@
           <t>(19) 99974-4496</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5519999744496</t>
-        </is>
+      <c r="I26" t="n">
+        <v>5519999744496</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2471,7 +2443,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dentista em Campinas</t>
+          <t>Dentista</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2509,10 +2481,8 @@
           <t>(19) 98242-4662</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5519982424662</t>
-        </is>
+      <c r="I28" t="n">
+        <v>5519982424662</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2549,7 +2519,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dentista 24 Horas em Campinas</t>
+          <t>Dentista 24 Horas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2587,10 +2557,8 @@
           <t>(19) 4560-3770</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>551945603770</t>
-        </is>
+      <c r="I29" t="n">
+        <v>551945603770</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2627,7 +2595,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Clnica Dentista Campinas</t>
+          <t>Clnica Dentista</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2665,10 +2633,8 @@
           <t>(19) 3232-2555</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>551932322555</t>
-        </is>
+      <c r="I30" t="n">
+        <v>551932322555</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2743,10 +2709,8 @@
           <t>(57) 3711-2900</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>555737112900</t>
-        </is>
+      <c r="I31" t="n">
+        <v>555737112900</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2895,10 +2859,8 @@
           <t>(19) 98604-9825</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5519986049825</t>
-        </is>
+      <c r="I33" t="n">
+        <v>5519986049825</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2935,7 +2897,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10 Melhores Barbearias em Campinas</t>
+          <t>10 Melhores Barbearias</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3009,7 +2971,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Encontrar seu smartphone</t>
+          <t>Encontrar Seu Smartphone</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
